--- a/outputs_xlsx_solution/test33.4-wide.xlsx
+++ b/outputs_xlsx_solution/test33.4-wide.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -864,7 +870,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -884,13 +890,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -910,16 +916,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -939,16 +945,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -968,16 +974,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -997,16 +1003,16 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1029,10 +1035,10 @@
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1052,13 +1058,13 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1078,13 +1084,16 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1095,7 +1104,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -1113,7 +1122,7 @@
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -1124,7 +1133,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1133,7 +1142,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N12" t="s">
         <v>14</v>
@@ -1145,7 +1154,7 @@
         <v>14</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1156,7 +1165,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1165,7 +1174,16 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S13" t="s">
+        <v>15</v>
       </c>
       <c r="T13" t="s">
         <v>14</v>
@@ -1180,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="X13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1191,7 +1209,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1212,10 +1230,10 @@
         <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1226,7 +1244,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1253,10 +1271,10 @@
         <v>14</v>
       </c>
       <c r="R15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1267,7 +1285,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1276,16 +1294,16 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
       </c>
       <c r="N16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -1305,16 +1323,19 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="M17" t="s">
+        <v>15</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1325,7 +1346,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
@@ -1334,16 +1355,16 @@
         <v>9</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M18" t="s">
         <v>14</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1354,7 +1375,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -1363,16 +1384,16 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N19" t="s">
         <v>14</v>
       </c>
       <c r="O19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1383,7 +1404,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
@@ -1392,13 +1413,13 @@
         <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P20" t="s">
         <v>14</v>
@@ -1413,10 +1434,10 @@
         <v>14</v>
       </c>
       <c r="T20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1427,7 +1448,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
@@ -1436,7 +1457,7 @@
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T21" t="s">
         <v>14</v>
@@ -1448,10 +1469,10 @@
         <v>14</v>
       </c>
       <c r="W21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1483,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>5</v>
@@ -1471,16 +1492,16 @@
         <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W22" t="s">
         <v>14</v>
       </c>
       <c r="X22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1491,7 +1512,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
         <v>5</v>
@@ -1500,16 +1521,16 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P23" t="s">
         <v>14</v>
       </c>
       <c r="Q23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1520,7 +1541,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>5</v>
@@ -1529,16 +1550,16 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q24" t="s">
         <v>14</v>
       </c>
       <c r="R24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1549,7 +1570,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>5</v>
@@ -1558,16 +1579,16 @@
         <v>9</v>
       </c>
       <c r="T25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U25" t="s">
         <v>14</v>
       </c>
       <c r="V25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1578,7 +1599,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R26" t="s">
         <v>5</v>
@@ -1587,7 +1608,13 @@
         <v>9</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="V26" t="s">
+        <v>15</v>
+      </c>
+      <c r="W26" t="s">
+        <v>15</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1602,7 +1629,7 @@
         <v>14</v>
       </c>
       <c r="AB26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1613,7 +1640,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R27" t="s">
         <v>5</v>
@@ -1622,7 +1649,7 @@
         <v>9</v>
       </c>
       <c r="T27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB27" t="s">
         <v>14</v>
@@ -1634,7 +1661,7 @@
         <v>14</v>
       </c>
       <c r="AE27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1645,7 +1672,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R28" t="s">
         <v>5</v>
@@ -1654,13 +1681,13 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE28" t="s">
         <v>14</v>
       </c>
       <c r="AF28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1671,7 +1698,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S29" t="s">
         <v>5</v>
@@ -1680,25 +1707,25 @@
         <v>9</v>
       </c>
       <c r="U29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y29" t="s">
         <v>14</v>
       </c>
       <c r="Z29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -1709,7 +1736,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S30" t="s">
         <v>5</v>
@@ -1718,16 +1745,16 @@
         <v>9</v>
       </c>
       <c r="X30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z30" t="s">
         <v>14</v>
       </c>
       <c r="AA30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1738,7 +1765,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
         <v>5</v>
@@ -1750,10 +1777,10 @@
         <v>14</v>
       </c>
       <c r="Y31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1764,7 +1791,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T32" t="s">
         <v>5</v>
@@ -1773,7 +1800,16 @@
         <v>9</v>
       </c>
       <c r="X32" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>15</v>
       </c>
       <c r="AB32" t="s">
         <v>14</v>
@@ -1788,10 +1824,10 @@
         <v>14</v>
       </c>
       <c r="AF32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1802,7 +1838,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T33" t="s">
         <v>5</v>
@@ -1811,7 +1847,7 @@
         <v>9</v>
       </c>
       <c r="Y33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF33" t="s">
         <v>14</v>
@@ -1823,7 +1859,7 @@
         <v>14</v>
       </c>
       <c r="AI33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1834,7 +1870,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T34" t="s">
         <v>5</v>
@@ -1843,13 +1879,13 @@
         <v>9</v>
       </c>
       <c r="Y34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI34" t="s">
         <v>14</v>
       </c>
       <c r="AJ34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -1860,7 +1896,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U35" t="s">
         <v>5</v>
@@ -1869,16 +1905,16 @@
         <v>9</v>
       </c>
       <c r="Y35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z35" t="s">
         <v>14</v>
       </c>
       <c r="AA35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -1889,7 +1925,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U36" t="s">
         <v>5</v>
@@ -1898,16 +1934,16 @@
         <v>9</v>
       </c>
       <c r="Y36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA36" t="s">
         <v>14</v>
       </c>
       <c r="AB36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -1918,7 +1954,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB37" t="s">
         <v>5</v>
@@ -1936,10 +1972,10 @@
         <v>14</v>
       </c>
       <c r="AG37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -1950,7 +1986,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AB38" t="s">
         <v>5</v>
@@ -1959,10 +1995,10 @@
         <v>9</v>
       </c>
       <c r="AD38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AG38" t="s">
         <v>14</v>
@@ -1974,10 +2010,10 @@
         <v>14</v>
       </c>
       <c r="AJ38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -1988,7 +2024,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AB39" t="s">
         <v>5</v>
@@ -2000,10 +2036,10 @@
         <v>14</v>
       </c>
       <c r="AF39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2014,7 +2050,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AB40" t="s">
         <v>5</v>
@@ -2023,10 +2059,10 @@
         <v>14</v>
       </c>
       <c r="AF40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2037,7 +2073,7 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC41" t="s">
         <v>5</v>
@@ -2046,13 +2082,13 @@
         <v>9</v>
       </c>
       <c r="AE41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="s">
         <v>14</v>
@@ -2064,7 +2100,7 @@
         <v>14</v>
       </c>
       <c r="AK41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2075,7 +2111,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC42" t="s">
         <v>5</v>
@@ -2084,13 +2120,13 @@
         <v>9</v>
       </c>
       <c r="AG42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK42" t="s">
         <v>14</v>
@@ -2102,7 +2138,7 @@
         <v>14</v>
       </c>
       <c r="AN42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2113,7 +2149,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC43" t="s">
         <v>5</v>
@@ -2122,7 +2158,7 @@
         <v>9</v>
       </c>
       <c r="AI43" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN43" t="s">
         <v>14</v>
@@ -2137,7 +2173,7 @@
         <v>14</v>
       </c>
       <c r="AR43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -2148,7 +2184,7 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC44" t="s">
         <v>5</v>
@@ -2169,10 +2205,10 @@
         <v>14</v>
       </c>
       <c r="AM44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -2183,7 +2219,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD45" t="s">
         <v>5</v>
@@ -2210,10 +2246,10 @@
         <v>14</v>
       </c>
       <c r="AO45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2224,7 +2260,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD46" t="s">
         <v>5</v>
@@ -2236,10 +2272,10 @@
         <v>14</v>
       </c>
       <c r="AK46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2259,16 +2295,16 @@
         <v>9</v>
       </c>
       <c r="AJ47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK47" t="s">
         <v>14</v>
       </c>
       <c r="AL47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -2279,7 +2315,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD48" t="s">
         <v>5</v>
@@ -2288,16 +2324,16 @@
         <v>9</v>
       </c>
       <c r="AJ48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK48" t="s">
         <v>14</v>
       </c>
       <c r="AL48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -2308,7 +2344,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE49" t="s">
         <v>5</v>
@@ -2317,16 +2353,19 @@
         <v>9</v>
       </c>
       <c r="AJ49" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>15</v>
       </c>
       <c r="AL49" t="s">
         <v>14</v>
       </c>
       <c r="AM49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -2337,7 +2376,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE50" t="s">
         <v>5</v>
@@ -2346,13 +2385,25 @@
         <v>9</v>
       </c>
       <c r="AK50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM50" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO50" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ50" t="s">
+        <v>15</v>
       </c>
       <c r="AR50" t="s">
         <v>14</v>
@@ -2367,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="AV50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -2378,7 +2429,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE51" t="s">
         <v>5</v>
@@ -2387,7 +2438,7 @@
         <v>9</v>
       </c>
       <c r="AM51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AV51" t="s">
         <v>14</v>
@@ -2399,7 +2450,7 @@
         <v>14</v>
       </c>
       <c r="AY51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2410,7 +2461,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE52" t="s">
         <v>5</v>
@@ -2419,13 +2470,13 @@
         <v>9</v>
       </c>
       <c r="AM52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AY52" t="s">
         <v>14</v>
       </c>
       <c r="AZ52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2436,7 +2487,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF53" t="s">
         <v>5</v>
@@ -2445,16 +2496,16 @@
         <v>9</v>
       </c>
       <c r="AM53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AN53" t="s">
         <v>14</v>
       </c>
       <c r="AO53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2465,7 +2516,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AF54" t="s">
         <v>5</v>
@@ -2474,16 +2525,16 @@
         <v>9</v>
       </c>
       <c r="AN54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO54" t="s">
         <v>14</v>
       </c>
       <c r="AP54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2494,7 +2545,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG55" t="s">
         <v>5</v>
@@ -2503,16 +2554,16 @@
         <v>9</v>
       </c>
       <c r="AN55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AO55" t="s">
         <v>14</v>
       </c>
       <c r="AP55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2523,7 +2574,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG56" t="s">
         <v>5</v>
@@ -2532,19 +2583,28 @@
         <v>9</v>
       </c>
       <c r="AN56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR56" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>15</v>
       </c>
       <c r="AV56" t="s">
         <v>14</v>
@@ -2559,10 +2619,10 @@
         <v>14</v>
       </c>
       <c r="AZ56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2573,7 +2633,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI57" t="s">
         <v>5</v>
@@ -2582,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="AR57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AZ57" t="s">
         <v>14</v>
@@ -2594,7 +2654,7 @@
         <v>14</v>
       </c>
       <c r="BC57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -2605,7 +2665,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI58" t="s">
         <v>5</v>
@@ -2614,13 +2674,13 @@
         <v>9</v>
       </c>
       <c r="AR58" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC58" t="s">
         <v>14</v>
       </c>
       <c r="BD58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -2631,7 +2691,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AJ59" t="s">
         <v>5</v>
@@ -2640,16 +2700,16 @@
         <v>9</v>
       </c>
       <c r="AR59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS59" t="s">
         <v>14</v>
       </c>
       <c r="AT59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -2660,7 +2720,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AJ60" t="s">
         <v>5</v>
@@ -2669,16 +2729,16 @@
         <v>9</v>
       </c>
       <c r="AS60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AT60" t="s">
         <v>14</v>
       </c>
       <c r="AU60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2689,7 +2749,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK61" t="s">
         <v>5</v>
@@ -2701,10 +2761,10 @@
         <v>14</v>
       </c>
       <c r="AT61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -2715,7 +2775,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK62" t="s">
         <v>5</v>
@@ -2724,16 +2784,25 @@
         <v>9</v>
       </c>
       <c r="AS62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV62" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AW62" t="s">
+        <v>15</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>15</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>15</v>
       </c>
       <c r="AZ62" t="s">
         <v>14</v>
@@ -2748,10 +2817,10 @@
         <v>14</v>
       </c>
       <c r="BD62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -2762,7 +2831,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK63" t="s">
         <v>5</v>
@@ -2771,7 +2840,7 @@
         <v>9</v>
       </c>
       <c r="AV63" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD63" t="s">
         <v>14</v>
@@ -2783,7 +2852,7 @@
         <v>14</v>
       </c>
       <c r="BG63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -2794,7 +2863,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK64" t="s">
         <v>5</v>
@@ -2803,25 +2872,25 @@
         <v>9</v>
       </c>
       <c r="AV64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BG64" t="s">
         <v>14</v>
       </c>
       <c r="BH64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -2832,7 +2901,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AL65" t="s">
         <v>5</v>
@@ -2841,16 +2910,16 @@
         <v>9</v>
       </c>
       <c r="AZ65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BA65" t="s">
         <v>14</v>
       </c>
       <c r="BB65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -2861,7 +2930,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AN66" t="s">
         <v>5</v>
@@ -2870,16 +2939,16 @@
         <v>9</v>
       </c>
       <c r="AZ66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BB66" t="s">
         <v>14</v>
       </c>
       <c r="BC66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -2890,7 +2959,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC67" t="s">
         <v>5</v>
@@ -2908,7 +2977,7 @@
         <v>14</v>
       </c>
       <c r="BH67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -2919,7 +2988,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BC68" t="s">
         <v>5</v>
@@ -2928,7 +2997,7 @@
         <v>9</v>
       </c>
       <c r="BE68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BH68" t="s">
         <v>14</v>
@@ -2940,7 +3009,7 @@
         <v>14</v>
       </c>
       <c r="BK68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -2951,7 +3020,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BC69" t="s">
         <v>5</v>
@@ -2963,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="BF69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -2977,7 +3046,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BC70" t="s">
         <v>5</v>
@@ -2989,10 +3058,10 @@
         <v>14</v>
       </c>
       <c r="BF70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -3003,7 +3072,7 @@
         <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD71" t="s">
         <v>5</v>
@@ -3012,7 +3081,7 @@
         <v>9</v>
       </c>
       <c r="BF71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG71" t="s">
         <v>14</v>
@@ -3024,10 +3093,10 @@
         <v>14</v>
       </c>
       <c r="BJ71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3038,7 +3107,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD72" t="s">
         <v>5</v>
@@ -3047,10 +3116,10 @@
         <v>9</v>
       </c>
       <c r="BG72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BJ72" t="s">
         <v>14</v>
@@ -3062,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="BM72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -3073,7 +3142,7 @@
         <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD73" t="s">
         <v>5</v>
@@ -3082,7 +3151,7 @@
         <v>9</v>
       </c>
       <c r="BH73" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BM73" t="s">
         <v>14</v>
@@ -3097,7 +3166,7 @@
         <v>14</v>
       </c>
       <c r="BQ73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -3108,7 +3177,7 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD74" t="s">
         <v>5</v>
@@ -3129,10 +3198,10 @@
         <v>14</v>
       </c>
       <c r="BL74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -3143,7 +3212,7 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE75" t="s">
         <v>5</v>
@@ -3170,10 +3239,10 @@
         <v>14</v>
       </c>
       <c r="BN75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -3184,7 +3253,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE76" t="s">
         <v>5</v>
@@ -3196,10 +3265,10 @@
         <v>14</v>
       </c>
       <c r="BJ76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3219,16 +3288,16 @@
         <v>9</v>
       </c>
       <c r="BI77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BJ77" t="s">
         <v>14</v>
       </c>
       <c r="BK77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -3239,7 +3308,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE78" t="s">
         <v>5</v>
@@ -3248,16 +3317,16 @@
         <v>9</v>
       </c>
       <c r="BI78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BJ78" t="s">
         <v>14</v>
       </c>
       <c r="BK78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -3268,7 +3337,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF79" t="s">
         <v>5</v>
@@ -3277,16 +3346,19 @@
         <v>9</v>
       </c>
       <c r="BI79" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BJ79" t="s">
+        <v>15</v>
       </c>
       <c r="BK79" t="s">
         <v>14</v>
       </c>
       <c r="BL79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -3297,7 +3369,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF80" t="s">
         <v>5</v>
@@ -3306,13 +3378,25 @@
         <v>9</v>
       </c>
       <c r="BJ80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BK80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BL80" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BM80" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN80" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO80" t="s">
+        <v>15</v>
+      </c>
+      <c r="BP80" t="s">
+        <v>15</v>
       </c>
       <c r="BQ80" t="s">
         <v>14</v>
@@ -3327,7 +3411,7 @@
         <v>14</v>
       </c>
       <c r="BU80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -3338,7 +3422,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF81" t="s">
         <v>5</v>
@@ -3347,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="BL81" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BU81" t="s">
         <v>14</v>
@@ -3359,7 +3443,7 @@
         <v>14</v>
       </c>
       <c r="BX81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3370,7 +3454,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF82" t="s">
         <v>5</v>
@@ -3379,13 +3463,13 @@
         <v>9</v>
       </c>
       <c r="BL82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BX82" t="s">
         <v>14</v>
       </c>
       <c r="BY82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -3396,7 +3480,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BG83" t="s">
         <v>5</v>
@@ -3405,16 +3489,16 @@
         <v>9</v>
       </c>
       <c r="BL83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BM83" t="s">
         <v>14</v>
       </c>
       <c r="BN83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -3425,7 +3509,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BG84" t="s">
         <v>5</v>
@@ -3434,16 +3518,16 @@
         <v>9</v>
       </c>
       <c r="BM84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BN84" t="s">
         <v>14</v>
       </c>
       <c r="BO84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -3454,7 +3538,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH85" t="s">
         <v>5</v>
@@ -3463,16 +3547,16 @@
         <v>9</v>
       </c>
       <c r="BM85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BN85" t="s">
         <v>14</v>
       </c>
       <c r="BO85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -3483,7 +3567,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH86" t="s">
         <v>5</v>
@@ -3492,19 +3576,28 @@
         <v>9</v>
       </c>
       <c r="BM86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BO86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BP86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BQ86" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BR86" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS86" t="s">
+        <v>15</v>
+      </c>
+      <c r="BT86" t="s">
+        <v>15</v>
       </c>
       <c r="BU86" t="s">
         <v>14</v>
@@ -3519,10 +3612,10 @@
         <v>14</v>
       </c>
       <c r="BY86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -3533,7 +3626,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH87" t="s">
         <v>5</v>
@@ -3542,7 +3635,7 @@
         <v>9</v>
       </c>
       <c r="BQ87" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BY87" t="s">
         <v>14</v>
@@ -3554,7 +3647,7 @@
         <v>14</v>
       </c>
       <c r="CB87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
@@ -3565,7 +3658,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH88" t="s">
         <v>5</v>
@@ -3574,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="BQ88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB88" t="s">
         <v>14</v>
       </c>
       <c r="CC88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
@@ -3591,7 +3684,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BI89" t="s">
         <v>5</v>
@@ -3600,16 +3693,16 @@
         <v>9</v>
       </c>
       <c r="BQ89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BR89" t="s">
         <v>14</v>
       </c>
       <c r="BS89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CC89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -3620,7 +3713,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BI90" t="s">
         <v>5</v>
@@ -3629,16 +3722,16 @@
         <v>9</v>
       </c>
       <c r="BR90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BS90" t="s">
         <v>14</v>
       </c>
       <c r="BT90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CC90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -3649,7 +3742,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BK91" t="s">
         <v>5</v>
@@ -3661,10 +3754,10 @@
         <v>14</v>
       </c>
       <c r="BS91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CC91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -3675,7 +3768,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BK92" t="s">
         <v>5</v>
@@ -3684,16 +3777,25 @@
         <v>9</v>
       </c>
       <c r="BR92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BS92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BT92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BU92" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BV92" t="s">
+        <v>15</v>
+      </c>
+      <c r="BW92" t="s">
+        <v>15</v>
+      </c>
+      <c r="BX92" t="s">
+        <v>15</v>
       </c>
       <c r="BY92" t="s">
         <v>14</v>
@@ -3708,10 +3810,10 @@
         <v>14</v>
       </c>
       <c r="CC92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CD92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -3722,7 +3824,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BK93" t="s">
         <v>5</v>
@@ -3731,7 +3833,7 @@
         <v>9</v>
       </c>
       <c r="BU93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC93" t="s">
         <v>14</v>
@@ -3743,7 +3845,7 @@
         <v>14</v>
       </c>
       <c r="CF93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -3754,7 +3856,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BK94" t="s">
         <v>5</v>
@@ -3763,25 +3865,25 @@
         <v>9</v>
       </c>
       <c r="BU94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BX94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BY94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CF94" t="s">
         <v>14</v>
       </c>
       <c r="CG94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3894,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BL95" t="s">
         <v>5</v>
@@ -3801,16 +3903,16 @@
         <v>9</v>
       </c>
       <c r="BY95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BZ95" t="s">
         <v>14</v>
       </c>
       <c r="CA95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CG95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -3821,7 +3923,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BM96" t="s">
         <v>5</v>
@@ -3830,16 +3932,16 @@
         <v>9</v>
       </c>
       <c r="BY96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA96" t="s">
         <v>14</v>
       </c>
       <c r="CB96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CG96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -3850,7 +3952,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CB97" t="s">
         <v>5</v>
@@ -3868,7 +3970,7 @@
         <v>14</v>
       </c>
       <c r="CG97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -3879,7 +3981,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CB98" t="s">
         <v>5</v>
@@ -3888,7 +3990,7 @@
         <v>9</v>
       </c>
       <c r="CD98" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CG98" t="s">
         <v>14</v>
@@ -3900,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="CJ98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -3911,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CB99" t="s">
         <v>5</v>
@@ -3923,10 +4025,10 @@
         <v>14</v>
       </c>
       <c r="CE99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CJ99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -3937,7 +4039,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CB100" t="s">
         <v>5</v>
@@ -3946,10 +4048,10 @@
         <v>14</v>
       </c>
       <c r="CE100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CJ100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -3960,7 +4062,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CC101" t="s">
         <v>5</v>
@@ -3972,10 +4074,10 @@
         <v>14</v>
       </c>
       <c r="CF101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CJ101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -3986,7 +4088,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CC102" t="s">
         <v>5</v>
@@ -3995,19 +4097,19 @@
         <v>9</v>
       </c>
       <c r="CE102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CF102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CG102" t="s">
         <v>14</v>
       </c>
       <c r="CH102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -4018,7 +4120,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CC103" t="s">
         <v>5</v>
@@ -4027,19 +4129,19 @@
         <v>9</v>
       </c>
       <c r="CF103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CG103" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CH103" t="s">
         <v>14</v>
       </c>
       <c r="CI103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -4050,7 +4152,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CC104" t="s">
         <v>5</v>
@@ -4059,19 +4161,19 @@
         <v>9</v>
       </c>
       <c r="CG104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CH104" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CI104" t="s">
         <v>14</v>
       </c>
       <c r="CJ104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -4082,7 +4184,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CD105" t="s">
         <v>5</v>
@@ -4091,16 +4193,16 @@
         <v>9</v>
       </c>
       <c r="CH105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CI105" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CJ105" t="s">
         <v>14</v>
       </c>
       <c r="CK105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
@@ -4111,7 +4213,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CD106" t="s">
         <v>5</v>
@@ -4120,16 +4222,16 @@
         <v>9</v>
       </c>
       <c r="CI106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CJ106" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CK106" t="s">
         <v>14</v>
       </c>
       <c r="CL106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -4140,7 +4242,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CD107" t="s">
         <v>5</v>
@@ -4149,16 +4251,16 @@
         <v>9</v>
       </c>
       <c r="CJ107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CK107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CL107" t="s">
         <v>14</v>
       </c>
       <c r="CM107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -4169,7 +4271,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CD108" t="s">
         <v>5</v>
@@ -4178,16 +4280,16 @@
         <v>9</v>
       </c>
       <c r="CK108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CL108" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CM108" t="s">
         <v>14</v>
       </c>
       <c r="CN108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -4198,7 +4300,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CE109" t="s">
         <v>5</v>
@@ -4207,21 +4309,21 @@
         <v>9</v>
       </c>
       <c r="CL109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CM109" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CN109" t="s">
         <v>14</v>
       </c>
       <c r="CO109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112">
@@ -4229,7 +4331,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113">
@@ -4237,15 +4339,15 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -4253,39 +4355,55 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
         <v>56</v>
       </c>
-      <c r="B119" t="s">
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>57</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
